--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/119.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/119.xlsx
@@ -426,13 +426,13 @@
         <v>0.7629924085314517</v>
       </c>
       <c r="E2">
-        <v>-14.52369674326393</v>
+        <v>-10.65199184940001</v>
       </c>
       <c r="F2">
-        <v>-5.651510633982038</v>
+        <v>-6.367078853313917</v>
       </c>
       <c r="G2">
-        <v>-12.72486753014995</v>
+        <v>-11.50579224076873</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>0.05543063981199577</v>
       </c>
       <c r="E3">
-        <v>-14.86329153757313</v>
+        <v>-12.24817025372763</v>
       </c>
       <c r="F3">
-        <v>-6.028704247421124</v>
+        <v>-5.711551300795221</v>
       </c>
       <c r="G3">
-        <v>-12.35123273949672</v>
+        <v>-11.61555999921434</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-0.8054353284115024</v>
       </c>
       <c r="E4">
-        <v>-15.71738890626381</v>
+        <v>-13.70258025077111</v>
       </c>
       <c r="F4">
-        <v>-6.050671832174185</v>
+        <v>-5.86074194100032</v>
       </c>
       <c r="G4">
-        <v>-12.1276848414119</v>
+        <v>-11.28302232088563</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.701301148971086</v>
       </c>
       <c r="E5">
-        <v>-15.92987396365172</v>
+        <v>-14.33026297602629</v>
       </c>
       <c r="F5">
-        <v>-5.962009640204223</v>
+        <v>-6.264889437267229</v>
       </c>
       <c r="G5">
-        <v>-11.68764381778643</v>
+        <v>-11.19576627210706</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.605660083564238</v>
       </c>
       <c r="E6">
-        <v>-16.398217802473</v>
+        <v>-13.82106777318181</v>
       </c>
       <c r="F6">
-        <v>-5.650612672727983</v>
+        <v>-6.044791532110158</v>
       </c>
       <c r="G6">
-        <v>-12.45146943733478</v>
+        <v>-11.88817349273671</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.461228924871965</v>
       </c>
       <c r="E7">
-        <v>-16.7720478602802</v>
+        <v>-15.39962135667157</v>
       </c>
       <c r="F7">
-        <v>-5.704742949064746</v>
+        <v>-5.868943953936381</v>
       </c>
       <c r="G7">
-        <v>-12.84633144598581</v>
+        <v>-11.98439118829008</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.226158343871735</v>
       </c>
       <c r="E8">
-        <v>-18.8511563182078</v>
+        <v>-14.67173708704868</v>
       </c>
       <c r="F8">
-        <v>-5.623532885279885</v>
+        <v>-5.444714274808743</v>
       </c>
       <c r="G8">
-        <v>-12.95404997674262</v>
+        <v>-12.19864638504618</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.852498694082032</v>
       </c>
       <c r="E9">
-        <v>-19.27686910272088</v>
+        <v>-17.87175154525088</v>
       </c>
       <c r="F9">
-        <v>-5.309000180091076</v>
+        <v>-5.861422142691001</v>
       </c>
       <c r="G9">
-        <v>-12.69458597010223</v>
+        <v>-12.16802714935346</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.303672859055256</v>
       </c>
       <c r="E10">
-        <v>-19.71124032953662</v>
+        <v>-17.23911919790532</v>
       </c>
       <c r="F10">
-        <v>-5.486498771681698</v>
+        <v>-5.543432207488788</v>
       </c>
       <c r="G10">
-        <v>-12.56575277989596</v>
+        <v>-11.40531387310631</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.550439129358001</v>
       </c>
       <c r="E11">
-        <v>-20.57779100174839</v>
+        <v>-17.61551690047487</v>
       </c>
       <c r="F11">
-        <v>-5.105861389729489</v>
+        <v>-5.351080829970217</v>
       </c>
       <c r="G11">
-        <v>-12.11961042084162</v>
+        <v>-11.84501391054123</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.581018131890821</v>
       </c>
       <c r="E12">
-        <v>-20.56566374835585</v>
+        <v>-19.46466491981897</v>
       </c>
       <c r="F12">
-        <v>-5.087778635587001</v>
+        <v>-5.273954351888316</v>
       </c>
       <c r="G12">
-        <v>-12.38705946332272</v>
+        <v>-11.14366490641001</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.400497056197783</v>
       </c>
       <c r="E13">
-        <v>-21.17378346589788</v>
+        <v>-20.19769353591458</v>
       </c>
       <c r="F13">
-        <v>-4.967822414727955</v>
+        <v>-5.134441738532466</v>
       </c>
       <c r="G13">
-        <v>-11.57336047522525</v>
+        <v>-10.75345752478719</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.032899232303234</v>
       </c>
       <c r="E14">
-        <v>-23.38714759273089</v>
+        <v>-20.69432222338777</v>
       </c>
       <c r="F14">
-        <v>-5.039217461101881</v>
+        <v>-5.446390627520236</v>
       </c>
       <c r="G14">
-        <v>-11.07421959263272</v>
+        <v>-9.61846016046684</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.517039501096439</v>
       </c>
       <c r="E15">
-        <v>-22.19173008113409</v>
+        <v>-21.21745606922786</v>
       </c>
       <c r="F15">
-        <v>-4.951720084832725</v>
+        <v>-5.088661551634858</v>
       </c>
       <c r="G15">
-        <v>-9.9555034912745</v>
+        <v>-9.315909403632848</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.904292062741387</v>
       </c>
       <c r="E16">
-        <v>-23.93358496581445</v>
+        <v>-21.52232199637224</v>
       </c>
       <c r="F16">
-        <v>-4.560851170813819</v>
+        <v>-4.629930839139372</v>
       </c>
       <c r="G16">
-        <v>-9.918554492510696</v>
+        <v>-8.116399438388719</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.250691631925375</v>
       </c>
       <c r="E17">
-        <v>-24.08477259903454</v>
+        <v>-22.48347701907825</v>
       </c>
       <c r="F17">
-        <v>-4.839215200305822</v>
+        <v>-4.875989643515283</v>
       </c>
       <c r="G17">
-        <v>-9.820532549638415</v>
+        <v>-8.294053243662628</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.611386288748657</v>
       </c>
       <c r="E18">
-        <v>-24.5429500137086</v>
+        <v>-23.03366396864016</v>
       </c>
       <c r="F18">
-        <v>-4.618182116805684</v>
+        <v>-4.144008687928748</v>
       </c>
       <c r="G18">
-        <v>-8.758466503548208</v>
+        <v>-7.526384080743189</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.033109166289659</v>
       </c>
       <c r="E19">
-        <v>-25.50257894067402</v>
+        <v>-23.88508500919231</v>
       </c>
       <c r="F19">
-        <v>-4.104377239247833</v>
+        <v>-3.647744937090305</v>
       </c>
       <c r="G19">
-        <v>-8.533091184325704</v>
+        <v>-7.005893489967894</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.547698221899294</v>
       </c>
       <c r="E20">
-        <v>-26.61552388364314</v>
+        <v>-24.52645731137266</v>
       </c>
       <c r="F20">
-        <v>-3.906082213428618</v>
+        <v>-3.832296562975336</v>
       </c>
       <c r="G20">
-        <v>-8.181279509867354</v>
+        <v>-6.053452848865113</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.175219373900457</v>
       </c>
       <c r="E21">
-        <v>-28.18637000437185</v>
+        <v>-26.04370894222059</v>
       </c>
       <c r="F21">
-        <v>-3.933773311360077</v>
+        <v>-4.025887982225697</v>
       </c>
       <c r="G21">
-        <v>-7.633817904583617</v>
+        <v>-6.663768471757453</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.9161422491480768</v>
       </c>
       <c r="E22">
-        <v>-27.70084513516546</v>
+        <v>-26.2636886240912</v>
       </c>
       <c r="F22">
-        <v>-3.639030595290599</v>
+        <v>-3.215542882384344</v>
       </c>
       <c r="G22">
-        <v>-7.464433842066807</v>
+        <v>-6.459487948711185</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.7657823720205675</v>
       </c>
       <c r="E23">
-        <v>-28.19262382697644</v>
+        <v>-27.28963252442495</v>
       </c>
       <c r="F23">
-        <v>-3.263623402124128</v>
+        <v>-3.520684211494598</v>
       </c>
       <c r="G23">
-        <v>-7.405684900926901</v>
+        <v>-6.65092686561062</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.703757169338633</v>
       </c>
       <c r="E24">
-        <v>-29.26147954700687</v>
+        <v>-28.16902142044846</v>
       </c>
       <c r="F24">
-        <v>-3.295185869165879</v>
+        <v>-3.851914720002843</v>
       </c>
       <c r="G24">
-        <v>-7.488749799052754</v>
+        <v>-7.050751382025019</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.7151313268727307</v>
       </c>
       <c r="E25">
-        <v>-28.40786219656101</v>
+        <v>-28.54176464449382</v>
       </c>
       <c r="F25">
-        <v>-3.23459169713525</v>
+        <v>-3.179025791386142</v>
       </c>
       <c r="G25">
-        <v>-7.175294105212402</v>
+        <v>-6.987854327324405</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.7761086527134015</v>
       </c>
       <c r="E26">
-        <v>-29.26541026244553</v>
+        <v>-29.28223354338403</v>
       </c>
       <c r="F26">
-        <v>-2.962982965225554</v>
+        <v>-2.982452253897009</v>
       </c>
       <c r="G26">
-        <v>-7.593809961741525</v>
+        <v>-6.872829422562428</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.8704078710104477</v>
       </c>
       <c r="E27">
-        <v>-29.58452729729206</v>
+        <v>-27.39102052898268</v>
       </c>
       <c r="F27">
-        <v>-2.959433880269054</v>
+        <v>-2.622489360817904</v>
       </c>
       <c r="G27">
-        <v>-7.602039977952153</v>
+        <v>-6.794611163106068</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.979698517122347</v>
       </c>
       <c r="E28">
-        <v>-30.03682901694117</v>
+        <v>-29.28359208558633</v>
       </c>
       <c r="F28">
-        <v>-2.921717132039906</v>
+        <v>-2.689288492625224</v>
       </c>
       <c r="G28">
-        <v>-7.901154388516384</v>
+        <v>-6.563545016101557</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.093785557132942</v>
       </c>
       <c r="E29">
-        <v>-29.74201856633081</v>
+        <v>-28.9673642171567</v>
       </c>
       <c r="F29">
-        <v>-2.637894860110341</v>
+        <v>-2.762355932445854</v>
       </c>
       <c r="G29">
-        <v>-8.506183070182507</v>
+        <v>-7.707050482457835</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.205160754204452</v>
       </c>
       <c r="E30">
-        <v>-30.592875811869</v>
+        <v>-28.15002900046029</v>
       </c>
       <c r="F30">
-        <v>-3.090579775273637</v>
+        <v>-3.221867411957652</v>
       </c>
       <c r="G30">
-        <v>-8.024856233136791</v>
+        <v>-8.005784180285049</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.312491525384929</v>
       </c>
       <c r="E31">
-        <v>-27.97737640044385</v>
+        <v>-28.47506927930885</v>
       </c>
       <c r="F31">
-        <v>-2.923946989968845</v>
+        <v>-2.975990733762016</v>
       </c>
       <c r="G31">
-        <v>-8.738123201209387</v>
+        <v>-8.389456545013344</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.416836232019991</v>
       </c>
       <c r="E32">
-        <v>-29.04590607034573</v>
+        <v>-28.03448951462859</v>
       </c>
       <c r="F32">
-        <v>-2.812538821788384</v>
+        <v>-2.635645205857459</v>
       </c>
       <c r="G32">
-        <v>-8.665609011717191</v>
+        <v>-7.134365830710391</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.52034422847603</v>
       </c>
       <c r="E33">
-        <v>-27.98331775834192</v>
+        <v>-28.10777380949472</v>
       </c>
       <c r="F33">
-        <v>-2.742931779392989</v>
+        <v>-2.819804072675462</v>
       </c>
       <c r="G33">
-        <v>-7.998199720454579</v>
+        <v>-7.822164771949374</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.625664059943292</v>
       </c>
       <c r="E34">
-        <v>-27.63586153315539</v>
+        <v>-28.54461758311865</v>
       </c>
       <c r="F34">
-        <v>-3.133898883178652</v>
+        <v>-2.712476322786131</v>
       </c>
       <c r="G34">
-        <v>-8.588734833749774</v>
+        <v>-7.863682323557373</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.732608346782387</v>
       </c>
       <c r="E35">
-        <v>-28.19961579084428</v>
+        <v>-26.08816497155389</v>
       </c>
       <c r="F35">
-        <v>-2.990522819242088</v>
+        <v>-2.723821200111381</v>
       </c>
       <c r="G35">
-        <v>-7.991873267929032</v>
+        <v>-7.627335856417725</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.842095383522185</v>
       </c>
       <c r="E36">
-        <v>-26.3053732273318</v>
+        <v>-26.71853761036962</v>
       </c>
       <c r="F36">
-        <v>-2.990537864448285</v>
+        <v>-2.94515597958841</v>
       </c>
       <c r="G36">
-        <v>-7.812878691711718</v>
+        <v>-8.255829684866203</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.950974403733906</v>
       </c>
       <c r="E37">
-        <v>-26.85930975337206</v>
+        <v>-25.57012565897244</v>
       </c>
       <c r="F37">
-        <v>-3.291708842828532</v>
+        <v>-2.578433829662209</v>
       </c>
       <c r="G37">
-        <v>-7.532852886726925</v>
+        <v>-7.479791462823487</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.059932042787659</v>
       </c>
       <c r="E38">
-        <v>-27.1148470131509</v>
+        <v>-25.1524056310829</v>
       </c>
       <c r="F38">
-        <v>-3.170149911583061</v>
+        <v>-2.813493796455394</v>
       </c>
       <c r="G38">
-        <v>-8.715644596997734</v>
+        <v>-7.612531096766104</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.165202485766461</v>
       </c>
       <c r="E39">
-        <v>-26.23215233110178</v>
+        <v>-25.24888024134231</v>
       </c>
       <c r="F39">
-        <v>-3.283222554680649</v>
+        <v>-3.041106386181224</v>
       </c>
       <c r="G39">
-        <v>-8.531737171200142</v>
+        <v>-7.73750750141913</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.268849769712303</v>
       </c>
       <c r="E40">
-        <v>-26.43380980713735</v>
+        <v>-23.96003578249326</v>
       </c>
       <c r="F40">
-        <v>-3.034952104993827</v>
+        <v>-2.67742732717154</v>
       </c>
       <c r="G40">
-        <v>-7.640594591302506</v>
+        <v>-8.546853122132454</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.370546230337018</v>
       </c>
       <c r="E41">
-        <v>-25.37371215583775</v>
+        <v>-24.33243031404002</v>
       </c>
       <c r="F41">
-        <v>-3.404571644892324</v>
+        <v>-2.724188619883763</v>
       </c>
       <c r="G41">
-        <v>-7.900866371054467</v>
+        <v>-6.545201283268455</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.473715631499475</v>
       </c>
       <c r="E42">
-        <v>-24.94721594532135</v>
+        <v>-24.2742031952494</v>
       </c>
       <c r="F42">
-        <v>-3.20657118837338</v>
+        <v>-2.628798845185015</v>
       </c>
       <c r="G42">
-        <v>-8.167497708787369</v>
+        <v>-7.461993970004364</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.579789484991819</v>
       </c>
       <c r="E43">
-        <v>-23.87483707251295</v>
+        <v>-23.81132522455537</v>
       </c>
       <c r="F43">
-        <v>-3.115861264654755</v>
+        <v>-2.994938983187291</v>
       </c>
       <c r="G43">
-        <v>-8.216222318034362</v>
+        <v>-6.793442540530705</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.690198489841332</v>
       </c>
       <c r="E44">
-        <v>-23.88204640313316</v>
+        <v>-22.39227808103778</v>
       </c>
       <c r="F44">
-        <v>-3.292533161757518</v>
+        <v>-2.697435075854245</v>
       </c>
       <c r="G44">
-        <v>-8.058911815099274</v>
+        <v>-7.619115771843714</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.805940360494816</v>
       </c>
       <c r="E45">
-        <v>-23.14981026998889</v>
+        <v>-21.83483198764157</v>
       </c>
       <c r="F45">
-        <v>-3.181953271770832</v>
+        <v>-3.369894820167862</v>
       </c>
       <c r="G45">
-        <v>-7.909059971264163</v>
+        <v>-7.33282972524416</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.923619977446799</v>
       </c>
       <c r="E46">
-        <v>-23.5142029879641</v>
+        <v>-21.51275333079403</v>
       </c>
       <c r="F46">
-        <v>-2.813276828744979</v>
+        <v>-3.045696757777125</v>
       </c>
       <c r="G46">
-        <v>-7.877947464286093</v>
+        <v>-6.981577532981947</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.041996130751281</v>
       </c>
       <c r="E47">
-        <v>-23.08516177505539</v>
+        <v>-21.88168357972493</v>
       </c>
       <c r="F47">
-        <v>-3.448762582903788</v>
+        <v>-3.118498926856919</v>
       </c>
       <c r="G47">
-        <v>-7.814616728119835</v>
+        <v>-7.29240465366412</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.15387351429335</v>
       </c>
       <c r="E48">
-        <v>-21.80316889737994</v>
+        <v>-20.39803322601391</v>
       </c>
       <c r="F48">
-        <v>-3.066354617738118</v>
+        <v>-3.029361623112325</v>
       </c>
       <c r="G48">
-        <v>-7.468101926524319</v>
+        <v>-7.038598369350354</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.257867461409915</v>
       </c>
       <c r="E49">
-        <v>-21.84120355057037</v>
+        <v>-21.22672132704755</v>
       </c>
       <c r="F49">
-        <v>-3.293609289927059</v>
+        <v>-2.959934331338333</v>
       </c>
       <c r="G49">
-        <v>-8.276699363945768</v>
+        <v>-6.463487087722624</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.347145234540782</v>
       </c>
       <c r="E50">
-        <v>-21.48797804949807</v>
+        <v>-20.12719878103717</v>
       </c>
       <c r="F50">
-        <v>-3.448016657417616</v>
+        <v>-3.307591829454474</v>
       </c>
       <c r="G50">
-        <v>-8.394342910229309</v>
+        <v>-6.859358812763134</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.420130813058522</v>
       </c>
       <c r="E51">
-        <v>-19.9107196095745</v>
+        <v>-18.93966081421371</v>
       </c>
       <c r="F51">
-        <v>-3.109154270102869</v>
+        <v>-3.157628340762639</v>
       </c>
       <c r="G51">
-        <v>-8.052327140021664</v>
+        <v>-8.063232077028022</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.471469519623938</v>
       </c>
       <c r="E52">
-        <v>-19.34293048154477</v>
+        <v>-19.12080883146854</v>
       </c>
       <c r="F52">
-        <v>-3.338616628337932</v>
+        <v>-3.2130509211264</v>
       </c>
       <c r="G52">
-        <v>-8.599116704560927</v>
+        <v>-6.696655431144573</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.49901201818836</v>
       </c>
       <c r="E53">
-        <v>-19.664823470958</v>
+        <v>-18.95385305175375</v>
       </c>
       <c r="F53">
-        <v>-3.155711264752</v>
+        <v>-3.4240892365942</v>
       </c>
       <c r="G53">
-        <v>-8.186390992179989</v>
+        <v>-6.624141241652377</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.500538664152586</v>
       </c>
       <c r="E54">
-        <v>-18.48360272537524</v>
+        <v>-17.93075303309682</v>
       </c>
       <c r="F54">
-        <v>-3.126460216493833</v>
+        <v>-3.162188621946147</v>
       </c>
       <c r="G54">
-        <v>-8.012838952829236</v>
+        <v>-7.568494220002719</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.474931513075539</v>
       </c>
       <c r="E55">
-        <v>-19.30006394658817</v>
+        <v>-17.79757514100524</v>
       </c>
       <c r="F55">
-        <v>-3.718844622311001</v>
+        <v>-3.633865338447393</v>
       </c>
       <c r="G55">
-        <v>-8.361141449015959</v>
+        <v>-6.892378193971824</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.425539046167123</v>
       </c>
       <c r="E56">
-        <v>-17.17704740468219</v>
+        <v>-17.02766210411716</v>
       </c>
       <c r="F56">
-        <v>-3.453364832294056</v>
+        <v>-3.604957954372877</v>
       </c>
       <c r="G56">
-        <v>-8.173453380212518</v>
+        <v>-7.804208372944366</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.354416048033803</v>
       </c>
       <c r="E57">
-        <v>-17.79833592463853</v>
+        <v>-16.64332145813816</v>
       </c>
       <c r="F57">
-        <v>-3.395596783469528</v>
+        <v>-3.472514212370592</v>
       </c>
       <c r="G57">
-        <v>-8.176803652298259</v>
+        <v>-7.078854603107892</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.269643803572131</v>
       </c>
       <c r="E58">
-        <v>-16.33949708001554</v>
+        <v>-16.17567500431406</v>
       </c>
       <c r="F58">
-        <v>-3.575900118236394</v>
+        <v>-3.71690379071163</v>
       </c>
       <c r="G58">
-        <v>-7.848430640257951</v>
+        <v>-7.914340291399301</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.173560674761316</v>
       </c>
       <c r="E59">
-        <v>-17.52035554767768</v>
+        <v>-15.11811329845875</v>
       </c>
       <c r="F59">
-        <v>-3.672095207393144</v>
+        <v>-3.580244223562445</v>
       </c>
       <c r="G59">
-        <v>-8.653359993221887</v>
+        <v>-7.811594200042481</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.073301793851551</v>
       </c>
       <c r="E60">
-        <v>-17.18655267162429</v>
+        <v>-15.46583670361173</v>
       </c>
       <c r="F60">
-        <v>-3.697456673922991</v>
+        <v>-3.859750896872437</v>
       </c>
       <c r="G60">
-        <v>-8.95341459871927</v>
+        <v>-8.127105742662721</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.970143446786165</v>
       </c>
       <c r="E61">
-        <v>-16.04469795059021</v>
+        <v>-13.73140851630394</v>
       </c>
       <c r="F61">
-        <v>-4.005077294643865</v>
+        <v>-4.194751417312386</v>
       </c>
       <c r="G61">
-        <v>-9.055088073321366</v>
+        <v>-7.779852689411948</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.869165122538368</v>
       </c>
       <c r="E62">
-        <v>-15.5254495354487</v>
+        <v>-14.00972400034136</v>
       </c>
       <c r="F62">
-        <v>-3.896359842813735</v>
+        <v>-3.850076829287975</v>
       </c>
       <c r="G62">
-        <v>-8.455124526330328</v>
+        <v>-8.923291944857441</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.771686574352689</v>
       </c>
       <c r="E63">
-        <v>-15.85465148191031</v>
+        <v>-14.56000151938342</v>
       </c>
       <c r="F63">
-        <v>-4.151679367530179</v>
+        <v>-4.074756395658412</v>
       </c>
       <c r="G63">
-        <v>-9.276758892085425</v>
+        <v>-7.863450585369624</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.678184187341493</v>
       </c>
       <c r="E64">
-        <v>-14.83473045200676</v>
+        <v>-14.32971050219735</v>
       </c>
       <c r="F64">
-        <v>-3.969447078958308</v>
+        <v>-4.161311466907882</v>
       </c>
       <c r="G64">
-        <v>-9.292834901224127</v>
+        <v>-8.862238864022203</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.586865432749171</v>
       </c>
       <c r="E65">
-        <v>-14.88985556610213</v>
+        <v>-13.65712342868212</v>
       </c>
       <c r="F65">
-        <v>-3.944970112182234</v>
+        <v>-4.215874886812517</v>
       </c>
       <c r="G65">
-        <v>-8.925612637280471</v>
+        <v>-9.134666966994367</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.492134939638479</v>
       </c>
       <c r="E66">
-        <v>-15.28481548362911</v>
+        <v>-13.81373617376339</v>
       </c>
       <c r="F66">
-        <v>-4.225729496871339</v>
+        <v>-4.457710739364909</v>
       </c>
       <c r="G66">
-        <v>-10.00438369616184</v>
+        <v>-9.046798467291032</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.390766649969227</v>
       </c>
       <c r="E67">
-        <v>-15.0330640281207</v>
+        <v>-12.91123394640473</v>
       </c>
       <c r="F67">
-        <v>-4.027265806372129</v>
+        <v>-4.37514898258122</v>
       </c>
       <c r="G67">
-        <v>-10.17066246696281</v>
+        <v>-9.875646511776202</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.276322042800031</v>
       </c>
       <c r="E68">
-        <v>-14.88692111494516</v>
+        <v>-13.77935599909716</v>
       </c>
       <c r="F68">
-        <v>-4.096792079765836</v>
+        <v>-4.420754169975172</v>
       </c>
       <c r="G68">
-        <v>-10.50224339763068</v>
+        <v>-8.095261605120472</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.149139288063086</v>
       </c>
       <c r="E69">
-        <v>-14.40977392265296</v>
+        <v>-13.39615652856809</v>
       </c>
       <c r="F69">
-        <v>-4.189572698968899</v>
+        <v>-4.900659030560083</v>
       </c>
       <c r="G69">
-        <v>-9.961522063064896</v>
+        <v>-9.868720850508046</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.007147792007748</v>
       </c>
       <c r="E70">
-        <v>-14.34359027503086</v>
+        <v>-11.97400285188124</v>
       </c>
       <c r="F70">
-        <v>-4.072744297292846</v>
+        <v>-4.236050508322258</v>
       </c>
       <c r="G70">
-        <v>-9.709619342436213</v>
+        <v>-8.854667646373889</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.855141731202949</v>
       </c>
       <c r="E71">
-        <v>-15.36213917731009</v>
+        <v>-13.04534923261589</v>
       </c>
       <c r="F71">
-        <v>-4.369343116695219</v>
+        <v>-4.483255915780948</v>
       </c>
       <c r="G71">
-        <v>-9.09322886847931</v>
+        <v>-9.505332198298866</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.696179937639881</v>
       </c>
       <c r="E72">
-        <v>-13.92536305805246</v>
+        <v>-13.75016545564371</v>
       </c>
       <c r="F72">
-        <v>-4.417604970762321</v>
+        <v>-4.384473843011327</v>
       </c>
       <c r="G72">
-        <v>-10.09169933476012</v>
+        <v>-8.783262489637348</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.534358648729001</v>
       </c>
       <c r="E73">
-        <v>-15.87296010232332</v>
+        <v>-14.2835744090072</v>
       </c>
       <c r="F73">
-        <v>-4.38675437952956</v>
+        <v>-4.450595940539798</v>
       </c>
       <c r="G73">
-        <v>-10.13434578239701</v>
+        <v>-9.125652351490931</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.372330582560476</v>
       </c>
       <c r="E74">
-        <v>-14.7891196618015</v>
+        <v>-12.81794738184672</v>
       </c>
       <c r="F74">
-        <v>-4.564626725716226</v>
+        <v>-4.662874297739386</v>
       </c>
       <c r="G74">
-        <v>-9.869826572718162</v>
+        <v>-8.336272630924952</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.210166743591492</v>
       </c>
       <c r="E75">
-        <v>-14.88536331988652</v>
+        <v>-14.09248639130554</v>
       </c>
       <c r="F75">
-        <v>-4.796181951318544</v>
+        <v>-5.09753347217315</v>
       </c>
       <c r="G75">
-        <v>-10.10643457295541</v>
+        <v>-8.900432627908774</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.047740873140341</v>
       </c>
       <c r="E76">
-        <v>-15.91381146634651</v>
+        <v>-14.67260655405815</v>
       </c>
       <c r="F76">
-        <v>-4.808423206191932</v>
+        <v>-4.829267151597989</v>
       </c>
       <c r="G76">
-        <v>-9.799560243647132</v>
+        <v>-9.965031241336524</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.8803910459368086</v>
       </c>
       <c r="E77">
-        <v>-16.74275316192458</v>
+        <v>-14.50671496573516</v>
       </c>
       <c r="F77">
-        <v>-4.598679570310005</v>
+        <v>-5.25444705427489</v>
       </c>
       <c r="G77">
-        <v>-9.416463913842669</v>
+        <v>-8.502018403894104</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.7053027054865229</v>
       </c>
       <c r="E78">
-        <v>-16.62822352579659</v>
+        <v>-14.85521726841746</v>
       </c>
       <c r="F78">
-        <v>-4.701722603845115</v>
+        <v>-5.057176686182964</v>
       </c>
       <c r="G78">
-        <v>-8.990969427316761</v>
+        <v>-8.537990791723825</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.5163648826683882</v>
       </c>
       <c r="E79">
-        <v>-16.75248938104107</v>
+        <v>-15.03368895753376</v>
       </c>
       <c r="F79">
-        <v>-4.833431506302637</v>
+        <v>-5.221623165471493</v>
       </c>
       <c r="G79">
-        <v>-9.585795007630852</v>
+        <v>-7.575721140914948</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.3100028964019357</v>
       </c>
       <c r="E80">
-        <v>-17.91033867227024</v>
+        <v>-15.61650356232093</v>
       </c>
       <c r="F80">
-        <v>-4.880948226736525</v>
+        <v>-4.846323664307271</v>
       </c>
       <c r="G80">
-        <v>-9.219741366262559</v>
+        <v>-8.15981062204518</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.08143961754142658</v>
       </c>
       <c r="E81">
-        <v>-18.72732972494207</v>
+        <v>-18.21780847196904</v>
       </c>
       <c r="F81">
-        <v>-4.926337238273019</v>
+        <v>-5.509524271986272</v>
       </c>
       <c r="G81">
-        <v>-8.944631721403583</v>
+        <v>-7.773549410705176</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.1720934177668588</v>
       </c>
       <c r="E82">
-        <v>-18.92561801631593</v>
+        <v>-17.7019654692813</v>
       </c>
       <c r="F82">
-        <v>-5.257631886870839</v>
+        <v>-4.970299330779703</v>
       </c>
       <c r="G82">
-        <v>-8.834152195667025</v>
+        <v>-7.631066841240483</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.4492702544938345</v>
       </c>
       <c r="E83">
-        <v>-18.55946825042574</v>
+        <v>-18.45101129794203</v>
       </c>
       <c r="F83">
-        <v>-4.846989612644714</v>
+        <v>-5.279973226219943</v>
       </c>
       <c r="G83">
-        <v>-8.274752763168676</v>
+        <v>-6.720431769207618</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.7467459543669039</v>
       </c>
       <c r="E84">
-        <v>-20.14988190734159</v>
+        <v>-19.37088475159412</v>
       </c>
       <c r="F84">
-        <v>-4.958044614406032</v>
+        <v>-5.163011001394036</v>
       </c>
       <c r="G84">
-        <v>-8.766732935759768</v>
+        <v>-8.31525397729612</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.054655198788809</v>
       </c>
       <c r="E85">
-        <v>-21.18122827716649</v>
+        <v>-20.52388404716108</v>
       </c>
       <c r="F85">
-        <v>-5.254909496402199</v>
+        <v>-5.472083880439368</v>
       </c>
       <c r="G85">
-        <v>-8.096652034246965</v>
+        <v>-7.441551351299365</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.362099176995007</v>
       </c>
       <c r="E86">
-        <v>-22.80726743910069</v>
+        <v>-20.75552454960144</v>
       </c>
       <c r="F86">
-        <v>-5.45850518592039</v>
+        <v>-5.541734474747437</v>
       </c>
       <c r="G86">
-        <v>-8.487448692975772</v>
+        <v>-7.715257324849689</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.653000155192088</v>
       </c>
       <c r="E87">
-        <v>-23.51508151192159</v>
+        <v>-22.1970465096191</v>
       </c>
       <c r="F87">
-        <v>-5.464629376695394</v>
+        <v>-5.226744078549066</v>
       </c>
       <c r="G87">
-        <v>-8.992240676803842</v>
+        <v>-6.820747920138614</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.910584346044201</v>
       </c>
       <c r="E88">
-        <v>-24.32413414965797</v>
+        <v>-22.80901995854166</v>
       </c>
       <c r="F88">
-        <v>-5.402464960249608</v>
+        <v>-5.406343456036518</v>
       </c>
       <c r="G88">
-        <v>-8.405208120689197</v>
+        <v>-7.341268305823762</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.115319525180738</v>
       </c>
       <c r="E89">
-        <v>-25.8929288716612</v>
+        <v>-26.46694917992548</v>
       </c>
       <c r="F89">
-        <v>-5.538405524913183</v>
+        <v>-5.440976728848306</v>
       </c>
       <c r="G89">
-        <v>-8.297794160122004</v>
+        <v>-5.994194083712159</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.249336119533197</v>
       </c>
       <c r="E90">
-        <v>-27.97297925218241</v>
+        <v>-27.24010913267707</v>
       </c>
       <c r="F90">
-        <v>-5.264308791010332</v>
+        <v>-5.462626780565321</v>
       </c>
       <c r="G90">
-        <v>-8.147117990447615</v>
+        <v>-7.700181100463848</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.29615318627442</v>
       </c>
       <c r="E91">
-        <v>-29.31428608241032</v>
+        <v>-28.82055561830203</v>
       </c>
       <c r="F91">
-        <v>-5.395050841006478</v>
+        <v>-5.024949062656729</v>
       </c>
       <c r="G91">
-        <v>-8.306136734880967</v>
+        <v>-6.688388998933013</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.244905519525091</v>
       </c>
       <c r="E92">
-        <v>-30.96548771016813</v>
+        <v>-30.28958126520528</v>
       </c>
       <c r="F92">
-        <v>-5.271380037922769</v>
+        <v>-5.797847436127516</v>
       </c>
       <c r="G92">
-        <v>-8.341874073977399</v>
+        <v>-7.476974188569566</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.087770181594593</v>
       </c>
       <c r="E93">
-        <v>-32.89760869451777</v>
+        <v>-33.45406984481731</v>
       </c>
       <c r="F93">
-        <v>-5.12925906092419</v>
+        <v>-4.866692497938696</v>
       </c>
       <c r="G93">
-        <v>-9.164319523389619</v>
+        <v>-7.483188082546778</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.825437821964614</v>
       </c>
       <c r="E94">
-        <v>-35.70051673851336</v>
+        <v>-34.34815137475871</v>
       </c>
       <c r="F94">
-        <v>-5.341539793682652</v>
+        <v>-4.637830364245584</v>
       </c>
       <c r="G94">
-        <v>-9.104299332762633</v>
+        <v>-7.612388743307915</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.462623667004056</v>
       </c>
       <c r="E95">
-        <v>-36.49603829591481</v>
+        <v>-37.38399280052383</v>
       </c>
       <c r="F95">
-        <v>-5.386612855889016</v>
+        <v>-4.53532341516285</v>
       </c>
       <c r="G95">
-        <v>-9.209515091091749</v>
+        <v>-7.888196913275676</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.00948069861004</v>
       </c>
       <c r="E96">
-        <v>-38.61542526590365</v>
+        <v>-39.35180495276493</v>
       </c>
       <c r="F96">
-        <v>-4.942748390821761</v>
+        <v>-4.685226723029898</v>
       </c>
       <c r="G96">
-        <v>-9.069250587138368</v>
+        <v>-8.072233450349302</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.4861578646854623</v>
       </c>
       <c r="E97">
-        <v>-41.42916315548857</v>
+        <v>-41.86997387234322</v>
       </c>
       <c r="F97">
-        <v>-4.842696185907958</v>
+        <v>-4.316146434995608</v>
       </c>
       <c r="G97">
-        <v>-9.70708677509867</v>
+        <v>-9.242438466479802</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.09382125857960961</v>
       </c>
       <c r="E98">
-        <v>-44.20675250130727</v>
+        <v>-42.8817074212409</v>
       </c>
       <c r="F98">
-        <v>-4.886902169125619</v>
+        <v>-4.451802724447362</v>
       </c>
       <c r="G98">
-        <v>-10.32573173056782</v>
+        <v>-9.170003730080548</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.6929814473198369</v>
       </c>
       <c r="E99">
-        <v>-45.57654116880643</v>
+        <v>-45.7091824367281</v>
       </c>
       <c r="F99">
-        <v>-4.810877950360863</v>
+        <v>-4.288514726035978</v>
       </c>
       <c r="G99">
-        <v>-10.02251224353489</v>
+        <v>-9.958214828071164</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.304932332128799</v>
       </c>
       <c r="E100">
-        <v>-47.79836674932277</v>
+        <v>-48.33502714702377</v>
       </c>
       <c r="F100">
-        <v>-4.675711817889938</v>
+        <v>-3.965016661659866</v>
       </c>
       <c r="G100">
-        <v>-10.33777880578522</v>
+        <v>-9.892560088936339</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.866183112822564</v>
       </c>
       <c r="E101">
-        <v>-49.82961716181882</v>
+        <v>-50.95406442876741</v>
       </c>
       <c r="F101">
-        <v>-4.508201659507992</v>
+        <v>-3.594499952360273</v>
       </c>
       <c r="G101">
-        <v>-10.80087115800063</v>
+        <v>-10.45827604232362</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.410321640318254</v>
       </c>
       <c r="E102">
-        <v>-52.15876984055394</v>
+        <v>-54.14613933991566</v>
       </c>
       <c r="F102">
-        <v>-3.942478942777247</v>
+        <v>-3.394536492359142</v>
       </c>
       <c r="G102">
-        <v>-11.80769744122256</v>
+        <v>-10.66906840844563</v>
       </c>
     </row>
   </sheetData>
